--- a/Summer2コスト表_井上恋.xlsx
+++ b/Summer2コスト表_井上恋.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\井上　恋\Documents\GitHub\Summer2_ChangeCollidable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r_inoue\Documents\GitHub\Summer2_ChangeCollidable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F9D8EC-2527-48AF-8A22-5E44E55042A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4BBA2F-0F7B-4A46-94BD-DAA6DB720F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2055" yWindow="1980" windowWidth="21600" windowHeight="12645" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="K2までの予定" sheetId="8" r:id="rId4"/>
     <sheet name="クラス設計" sheetId="6" r:id="rId5"/>
     <sheet name="クラス図" sheetId="7" r:id="rId6"/>
+    <sheet name="敵のグループ化" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="289">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -2137,6 +2138,9 @@
       <t>カン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
   </si>
 </sst>
 </file>
@@ -6765,6 +6769,845 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8EFB184-F126-D00C-9ED9-DD215D5E1927}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1400175" y="609600"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>A  : Group1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4512E24F-C693-49C6-AE81-B81970688A40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="1847850"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>B : Group1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52F80661-CCC0-42CD-B1A7-2E0ADF5BE9DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1304925" y="3105150"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>C : Group1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9987F0F-179A-417C-AB52-7E6065BBF548}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4743450" y="552450"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>D  : Group2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E649AADF-E136-44A1-9767-D01780DA3A38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4895850" y="1619250"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>E : Group2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D680B39D-9D0F-410A-AA3D-BCDF093D613B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4905375" y="3009900"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>F  : Group2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="楕円 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9873821-2CC2-95A2-0B66-6BE03C29714C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="981075"/>
+          <a:ext cx="1638300" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>攻撃権</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{880A99C4-EB86-F3B2-C7AA-3F9113E61A25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6896099" y="457200"/>
+          <a:ext cx="5629276" cy="1962150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800" b="1"/>
+            <a:t>グループ化について</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" b="1"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>攻撃権を持っている敵は攻撃することができる。</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800" b="0"/>
+            <a:t>攻撃権は</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>グループ内で順番に回す。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>グループ内で死亡した敵が出た場合順番を再構成</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="楕円 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09AE595C-1837-434C-A993-B9B906789352}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5762625" y="1876425"/>
+          <a:ext cx="1638300" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>攻撃権</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30EEB4D2-FD67-74D8-CFBB-979686A28F06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="438150" y="3895725"/>
+          <a:ext cx="5838826" cy="1885950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>各敵が自身の更新タイミングでグループの仲間の状態を見る処理をするとグループの数によっては負荷が大きいので、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>外からグループを見て攻撃権を渡す</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>ことで解決したい。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>514349</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF32285E-BD86-0E80-CAAF-54DF9DE70B38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4010025" y="3095625"/>
+          <a:ext cx="8162924" cy="1924050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+            <a:t>考えてる実装方法</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>アクターマネージャー内で敵を生成し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>CSV</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>から座標や大きさ渡すときに、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>"</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>グループタグ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>"</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>も一緒に渡して各敵毎に持たせる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>グループマネージャーアクターマネージャーに持たせてその中に</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>map&lt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>グループ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>,list&lt;Actor&gt;&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を作って各グループ毎に攻撃権の順番を割り振って回していく</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -6820,7 +7663,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">3654 2265 24575,'-31'0'0,"-1"1"0,1 2 0,-44 9 0,27-5 0,0-2 0,0-1 0,-90-7 0,32 0 0,-107 17 0,-9-1 0,-473-14-570,663-1 570,0-1 0,0-2 0,-42-11 0,39 7 0,0 2 0,-46-4 0,2 4-296,-124-29-1,100 15 365,24 6-68,0-2 0,-109-41 0,33 1-99,-142-63-168,243 94-776,8 4-1413,-54-34 0,47 23 3124,28 18 685,1 0-1,-40-34 1,58 43-1146,-1-1 0,1 0 0,0 0 0,0-1 0,1 1 0,0-1 0,1 0 0,-1 0-1,1-1 1,1 0 0,0 1 0,-4-18 0,5 14-207,-8-36 0,2 0 0,-2-84 0,10 117 0,0-25 0,9-68 0,-7 94 0,1 0 0,1 0 0,0 1 0,1-1 0,1 1 0,0 0 0,0 1 0,13-18 0,23-32-452,64-83 1134,-88 123-2643,2 2 0,28-24 0,41-35 347,28-23 1558,-19 35 1888,2 4 0,188-87 0,-178 104-2326,2 5 0,1 4 0,131-23 0,-138 33-2142,-63 15 1568,1 2-1,55-6 1,90-1 963,479-21-635,-504 37 1171,239 9-1340,-327-3 2278,0 5 0,-1 2 0,93 29 1,-56-9-509,-49-16 1,0 4 1,75 34-1,-32-2-793,-2 5 0,96 70 0,-123-66 873,89 91 0,-140-126-991,35 33 49,103 128 0,-45-10 0,-106-155 0,0 1 0,-2 0 0,-1 1 0,-1 0 0,0 1 0,-2 0 0,7 47 0,-3-8 0,-6-36 0,0 0 0,0 37 0,-4 7-1213,-4 124-4358,-1-163 5571,-1 0 0,-16 56 0,-39 48-756,53-117 1900,-1-1 1,0-1-1,-1 1 0,-1-1 0,-1-1 0,-18 23 1,-18 16-1615,31-42 470,1 0 0,-2-1 0,0 0 0,0-2 0,-1 0 0,-33 14 0,-138 66 0,165-80 0,-1-2 0,0 0 0,0-2 0,-47 8 0,34-7 0,-42 13 0,11 4 0,20-7 0,-73 18 0,43-12 0,61-17 0,0-1 0,-1 0 0,-29 3 0,-31 4 0,54-8 0,0-1 0,-30 0 0,45-4 0,0 0 0,0-1 0,0-1 0,0 1 0,0-2 0,0 1 0,1-1 0,-1-1 0,-9-5 0,-27-13-109,7 3-310,2-1 1,-65-45-1,86 52-6407</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="809.61">5190 1439 24575,'8'1'0,"1"0"0,0 1 0,-1 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,0 1 0,-1-1 0,0 1 0,12 10 0,42 24 0,10 0 0,-45-24 0,44 19 0,-53-27 0,0 0 0,0-1 0,1-2 0,0 1 0,0-2 0,0-1 0,19 1 0,-2-1 0,-1 2 0,65 16 0,-65-11 0,1-2 0,62 4 0,-94-11 0,64 2 0,0-3 0,126-18 0,-105 3 0,-22 5 0,91-28 0,-129 29 0,-1-2 0,0 0 0,0-1 0,-2-2 0,1-1 0,-2-1 0,29-25 0,-47 35 0,0-1 0,0 1 0,-1-1 0,0 0 0,-1 0 0,0-1 0,0 1 0,0-1 0,1-9 0,-1 5 0,1 1 0,0 0 0,12-20 0,140-199 0,-127 185 0,-21 30 0,0 1 0,23-26 0,-12 15 0,-2-1 0,-1 0 0,0-2 0,-2 0 0,15-43 0,-26 61 0,2-5 0,-1-1 0,-1 0 0,0 0 0,1-28 0,5-24 0,-2 21 0,-3-1 0,-2 0 0,-6-86 0,0 26 0,3 30-1365,0 56-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.62">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.61">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1552.66">7387 135 24575,'3'1'0,"-1"-1"0,1 2 0,0-1 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 0 0,2 3 0,23 31 0,26 70 0,43 76 0,-6-49 0,-86-126-83,4 8-173,0 0-1,2 0 1,0-1-1,21 25 1,-19-28-6570</inkml:trace>
 </inkml:ink>
 </file>
@@ -7178,11 +8021,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>0.14887640449438203</v>
+        <v>0.13054187192118227</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -7222,7 +8065,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45852</v>
+        <v>45887</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -7287,11 +8130,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-147</v>
+        <v>-172</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.62585034013605445</v>
+        <v>-0.53488372093023251</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -7318,11 +8161,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-127</v>
+        <v>-152</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.72440944881889768</v>
+        <v>-0.60526315789473684</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -7349,11 +8192,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-116</v>
+        <v>-141</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.7931034482758621</v>
+        <v>-0.65248226950354615</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -8891,7 +9734,7 @@
       </c>
       <c r="C4">
         <f>SUMIF(作業工数見積もり!H3:H43,"完了",作業工数見積もり!F3:F43)</f>
-        <v>18.25</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -8903,11 +9746,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0.10252808988764045</v>
+        <v>0.10837438423645321</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -8925,7 +9768,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45852</v>
+        <v>45887</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -8946,11 +9789,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>8</v>
+        <v>-19</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>2.96875</v>
+        <v>-1.0526315789473684</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -8963,11 +9806,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>15</v>
+        <v>-12</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>1.5833333333333333</v>
+        <v>-1.6666666666666667</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -8980,11 +9823,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>0.79166666666666663</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -9129,7 +9972,7 @@
         <v>0.25</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="35" t="s">
@@ -9159,7 +10002,7 @@
         <v>0.25</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="39" t="s">
@@ -9189,7 +10032,7 @@
         <v>0.25</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="I5" s="34"/>
       <c r="J5" s="42" t="s">
@@ -9257,11 +10100,11 @@
       </c>
       <c r="K7" s="40">
         <f>COUNTIF(H3:H84,J7)</f>
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="L7" s="45">
         <f>K7/K3</f>
-        <v>0.53658536585365857</v>
+        <v>0.92682926829268297</v>
       </c>
       <c r="M7" s="38"/>
     </row>
@@ -9290,11 +10133,11 @@
       </c>
       <c r="K8" s="40">
         <f>COUNTIF(H3:H84,J8)</f>
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="L8" s="47">
         <f>(K8+K9)/K3</f>
-        <v>0.46341463414634149</v>
+        <v>7.3170731707317069E-2</v>
       </c>
       <c r="M8" s="38"/>
     </row>
@@ -9326,7 +10169,7 @@
       </c>
       <c r="K9" s="31">
         <f>COUNTIF(H3:H84,J9)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="41"/>
       <c r="M9" s="38"/>
@@ -9971,7 +10814,7 @@
         <v>0.5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -9991,7 +10834,7 @@
         <v>0.5</v>
       </c>
       <c r="H40" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -10011,7 +10854,7 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -10031,7 +10874,7 @@
         <v>0.5</v>
       </c>
       <c r="H42" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -10051,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -10277,7 +11120,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="2:8">
@@ -10297,7 +11140,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="2:8">
@@ -10337,7 +11180,7 @@
         <v>0.25</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -10357,7 +11200,7 @@
         <v>0.25</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="2:8" hidden="1">
@@ -10397,7 +11240,7 @@
         <v>0.5</v>
       </c>
       <c r="H60" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -10417,7 +11260,7 @@
         <v>0.25</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -10437,7 +11280,7 @@
         <v>0.25</v>
       </c>
       <c r="H62" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -10457,7 +11300,7 @@
         <v>0.25</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>134</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -10477,7 +11320,7 @@
         <v>0.25</v>
       </c>
       <c r="H64" s="27" t="s">
-        <v>134</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -10497,7 +11340,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -10517,7 +11360,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -10537,7 +11380,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -10557,7 +11400,7 @@
         <v>0.25</v>
       </c>
       <c r="H68" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -10577,7 +11420,7 @@
         <v>0.25</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>134</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -10597,7 +11440,7 @@
         <v>0.25</v>
       </c>
       <c r="H70" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -10617,7 +11460,7 @@
         <v>0.5</v>
       </c>
       <c r="H71" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -10637,7 +11480,7 @@
         <v>0.5</v>
       </c>
       <c r="H72" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -10657,7 +11500,7 @@
         <v>0.5</v>
       </c>
       <c r="H73" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -10677,7 +11520,7 @@
         <v>0.5</v>
       </c>
       <c r="H74" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -10697,7 +11540,7 @@
         <v>0.5</v>
       </c>
       <c r="H75" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -10717,7 +11560,7 @@
         <v>0.25</v>
       </c>
       <c r="H76" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -10737,7 +11580,7 @@
         <v>0.25</v>
       </c>
       <c r="H77" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -10757,7 +11600,7 @@
         <v>0.5</v>
       </c>
       <c r="H78" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" spans="2:8" hidden="1">
@@ -10797,7 +11640,7 @@
         <v>0.5</v>
       </c>
       <c r="H80" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="2:8" hidden="1">
@@ -10837,7 +11680,7 @@
         <v>0.25</v>
       </c>
       <c r="H82" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -10857,7 +11700,7 @@
         <v>0.5</v>
       </c>
       <c r="H83" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -10877,7 +11720,7 @@
         <v>0.25</v>
       </c>
       <c r="H84" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -10897,7 +11740,7 @@
         <v>0.25</v>
       </c>
       <c r="H85" s="27" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="2:8" hidden="1">
@@ -11391,7 +12234,39 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B974D74-E96D-4AFE-B790-D41C78814A70}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
+    <_x8a73__x7d30_ xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101009C7952A5A25B2543AB99BC9B879A46ED" ma:contentTypeVersion="16" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="18ce886227b4f7d0c1a56646945dc47e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xmlns:ns3="04574505-c322-4981-8ebb-5d25af8d4de8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5be0a050d98fc17aa9c3986a154fc28" ns2:_="" ns3:_="">
     <xsd:import namespace="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
@@ -11634,28 +12509,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
+    <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
-    <_x8a73__x7d30_ xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F472F951-64CD-40D8-896F-068DA14071AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11672,23 +12545,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
-    <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Summer2コスト表_井上恋.xlsx
+++ b/Summer2コスト表_井上恋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r_inoue\Documents\GitHub\Summer2_ChangeCollidable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4BBA2F-0F7B-4A46-94BD-DAA6DB720F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603024DF-8895-437F-8A0E-4483AE8A4D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1980" windowWidth="21600" windowHeight="12645" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -6773,16 +6773,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6797,7 +6797,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1400175" y="609600"/>
+          <a:off x="1162050" y="438150"/>
           <a:ext cx="1990725" cy="657225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6841,16 +6841,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6865,7 +6865,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1543050" y="1847850"/>
+          <a:off x="990600" y="1590675"/>
           <a:ext cx="1990725" cy="657225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6910,15 +6910,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6933,7 +6933,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1304925" y="3105150"/>
+          <a:off x="885825" y="2771775"/>
           <a:ext cx="1990725" cy="657225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7181,15 +7181,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7204,7 +7204,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1409700" y="981075"/>
+          <a:off x="1752600" y="809625"/>
           <a:ext cx="1638300" cy="571500"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -7469,16 +7469,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>514349</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7493,7 +7493,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4010025" y="3095625"/>
+          <a:off x="8524875" y="3733800"/>
           <a:ext cx="8162924" cy="1924050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7663,7 +7663,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">3654 2265 24575,'-31'0'0,"-1"1"0,1 2 0,-44 9 0,27-5 0,0-2 0,0-1 0,-90-7 0,32 0 0,-107 17 0,-9-1 0,-473-14-570,663-1 570,0-1 0,0-2 0,-42-11 0,39 7 0,0 2 0,-46-4 0,2 4-296,-124-29-1,100 15 365,24 6-68,0-2 0,-109-41 0,33 1-99,-142-63-168,243 94-776,8 4-1413,-54-34 0,47 23 3124,28 18 685,1 0-1,-40-34 1,58 43-1146,-1-1 0,1 0 0,0 0 0,0-1 0,1 1 0,0-1 0,1 0 0,-1 0-1,1-1 1,1 0 0,0 1 0,-4-18 0,5 14-207,-8-36 0,2 0 0,-2-84 0,10 117 0,0-25 0,9-68 0,-7 94 0,1 0 0,1 0 0,0 1 0,1-1 0,1 1 0,0 0 0,0 1 0,13-18 0,23-32-452,64-83 1134,-88 123-2643,2 2 0,28-24 0,41-35 347,28-23 1558,-19 35 1888,2 4 0,188-87 0,-178 104-2326,2 5 0,1 4 0,131-23 0,-138 33-2142,-63 15 1568,1 2-1,55-6 1,90-1 963,479-21-635,-504 37 1171,239 9-1340,-327-3 2278,0 5 0,-1 2 0,93 29 1,-56-9-509,-49-16 1,0 4 1,75 34-1,-32-2-793,-2 5 0,96 70 0,-123-66 873,89 91 0,-140-126-991,35 33 49,103 128 0,-45-10 0,-106-155 0,0 1 0,-2 0 0,-1 1 0,-1 0 0,0 1 0,-2 0 0,7 47 0,-3-8 0,-6-36 0,0 0 0,0 37 0,-4 7-1213,-4 124-4358,-1-163 5571,-1 0 0,-16 56 0,-39 48-756,53-117 1900,-1-1 1,0-1-1,-1 1 0,-1-1 0,-1-1 0,-18 23 1,-18 16-1615,31-42 470,1 0 0,-2-1 0,0 0 0,0-2 0,-1 0 0,-33 14 0,-138 66 0,165-80 0,-1-2 0,0 0 0,0-2 0,-47 8 0,34-7 0,-42 13 0,11 4 0,20-7 0,-73 18 0,43-12 0,61-17 0,0-1 0,-1 0 0,-29 3 0,-31 4 0,54-8 0,0-1 0,-30 0 0,45-4 0,0 0 0,0-1 0,0-1 0,0 1 0,0-2 0,0 1 0,1-1 0,-1-1 0,-9-5 0,-27-13-109,7 3-310,2-1 1,-65-45-1,86 52-6407</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="809.61">5190 1439 24575,'8'1'0,"1"0"0,0 1 0,-1 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,0 1 0,-1-1 0,0 1 0,12 10 0,42 24 0,10 0 0,-45-24 0,44 19 0,-53-27 0,0 0 0,0-1 0,1-2 0,0 1 0,0-2 0,0-1 0,19 1 0,-2-1 0,-1 2 0,65 16 0,-65-11 0,1-2 0,62 4 0,-94-11 0,64 2 0,0-3 0,126-18 0,-105 3 0,-22 5 0,91-28 0,-129 29 0,-1-2 0,0 0 0,0-1 0,-2-2 0,1-1 0,-2-1 0,29-25 0,-47 35 0,0-1 0,0 1 0,-1-1 0,0 0 0,-1 0 0,0-1 0,0 1 0,0-1 0,1-9 0,-1 5 0,1 1 0,0 0 0,12-20 0,140-199 0,-127 185 0,-21 30 0,0 1 0,23-26 0,-12 15 0,-2-1 0,-1 0 0,0-2 0,-2 0 0,15-43 0,-26 61 0,2-5 0,-1-1 0,-1 0 0,0 0 0,1-28 0,5-24 0,-2 21 0,-3-1 0,-2 0 0,-6-86 0,0 26 0,3 30-1365,0 56-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.61">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.6">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1552.66">7387 135 24575,'3'1'0,"-1"-1"0,1 2 0,0-1 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 0 0,2 3 0,23 31 0,26 70 0,43 76 0,-6-49 0,-86-126-83,4 8-173,0 0-1,2 0 1,0-1-1,21 25 1,-19-28-6570</inkml:trace>
 </inkml:ink>
 </file>
@@ -12258,15 +12258,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101009C7952A5A25B2543AB99BC9B879A46ED" ma:contentTypeVersion="16" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="18ce886227b4f7d0c1a56646945dc47e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xmlns:ns3="04574505-c322-4981-8ebb-5d25af8d4de8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5be0a050d98fc17aa9c3986a154fc28" ns2:_="" ns3:_="">
     <xsd:import namespace="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
@@ -12509,6 +12500,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -12521,14 +12521,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F472F951-64CD-40D8-896F-068DA14071AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12545,4 +12537,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Summer2コスト表_井上恋.xlsx
+++ b/Summer2コスト表_井上恋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r_inoue\Documents\GitHub\Summer2_ChangeCollidable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603024DF-8895-437F-8A0E-4483AE8A4D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC35B42A-FFC2-4A36-9962-E4D0BBB3277A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="2745" windowWidth="21600" windowHeight="12645" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -7605,6 +7605,508 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2431EE5-6747-468F-AE09-05BBED06B3B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="971550" y="6067425"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>A  : Group1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D95E582-B56C-43CB-B941-103AE4CEAAAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1047750" y="7058025"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>B : Group1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{637EF991-8232-43C8-B277-963DC0924171}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1009650" y="7962900"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>C : Group1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB96039E-65AB-425E-90B8-D8B3A8E32AB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1009650" y="8963025"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>D  : Group2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EDE8B13-EBF4-4BF6-B8B6-D1884A701F41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1057275" y="9896475"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>E : Group2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEEC05B1-D84A-4768-8142-32BC6207D9F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1143000" y="10896600"/>
+          <a:ext cx="1990725" cy="657225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>敵</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>F  : Group2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="正方形/長方形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{846E5799-6D9C-EE0D-ABFC-BC660F871734}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4314825" y="6267450"/>
+          <a:ext cx="4543425" cy="2305050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>攻撃が終わった後に攻撃権を失う</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>グループマネージャーに各グループの前のフレームの攻撃権所有者の</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を持たせる</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>毎フレーム攻撃権を持っているアクターの</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を確認してそれが攻撃権を失ったなら次のアクターに移す</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7663,7 +8165,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">3654 2265 24575,'-31'0'0,"-1"1"0,1 2 0,-44 9 0,27-5 0,0-2 0,0-1 0,-90-7 0,32 0 0,-107 17 0,-9-1 0,-473-14-570,663-1 570,0-1 0,0-2 0,-42-11 0,39 7 0,0 2 0,-46-4 0,2 4-296,-124-29-1,100 15 365,24 6-68,0-2 0,-109-41 0,33 1-99,-142-63-168,243 94-776,8 4-1413,-54-34 0,47 23 3124,28 18 685,1 0-1,-40-34 1,58 43-1146,-1-1 0,1 0 0,0 0 0,0-1 0,1 1 0,0-1 0,1 0 0,-1 0-1,1-1 1,1 0 0,0 1 0,-4-18 0,5 14-207,-8-36 0,2 0 0,-2-84 0,10 117 0,0-25 0,9-68 0,-7 94 0,1 0 0,1 0 0,0 1 0,1-1 0,1 1 0,0 0 0,0 1 0,13-18 0,23-32-452,64-83 1134,-88 123-2643,2 2 0,28-24 0,41-35 347,28-23 1558,-19 35 1888,2 4 0,188-87 0,-178 104-2326,2 5 0,1 4 0,131-23 0,-138 33-2142,-63 15 1568,1 2-1,55-6 1,90-1 963,479-21-635,-504 37 1171,239 9-1340,-327-3 2278,0 5 0,-1 2 0,93 29 1,-56-9-509,-49-16 1,0 4 1,75 34-1,-32-2-793,-2 5 0,96 70 0,-123-66 873,89 91 0,-140-126-991,35 33 49,103 128 0,-45-10 0,-106-155 0,0 1 0,-2 0 0,-1 1 0,-1 0 0,0 1 0,-2 0 0,7 47 0,-3-8 0,-6-36 0,0 0 0,0 37 0,-4 7-1213,-4 124-4358,-1-163 5571,-1 0 0,-16 56 0,-39 48-756,53-117 1900,-1-1 1,0-1-1,-1 1 0,-1-1 0,-1-1 0,-18 23 1,-18 16-1615,31-42 470,1 0 0,-2-1 0,0 0 0,0-2 0,-1 0 0,-33 14 0,-138 66 0,165-80 0,-1-2 0,0 0 0,0-2 0,-47 8 0,34-7 0,-42 13 0,11 4 0,20-7 0,-73 18 0,43-12 0,61-17 0,0-1 0,-1 0 0,-29 3 0,-31 4 0,54-8 0,0-1 0,-30 0 0,45-4 0,0 0 0,0-1 0,0-1 0,0 1 0,0-2 0,0 1 0,1-1 0,-1-1 0,-9-5 0,-27-13-109,7 3-310,2-1 1,-65-45-1,86 52-6407</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="809.61">5190 1439 24575,'8'1'0,"1"0"0,0 1 0,-1 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,0 1 0,-1-1 0,0 1 0,12 10 0,42 24 0,10 0 0,-45-24 0,44 19 0,-53-27 0,0 0 0,0-1 0,1-2 0,0 1 0,0-2 0,0-1 0,19 1 0,-2-1 0,-1 2 0,65 16 0,-65-11 0,1-2 0,62 4 0,-94-11 0,64 2 0,0-3 0,126-18 0,-105 3 0,-22 5 0,91-28 0,-129 29 0,-1-2 0,0 0 0,0-1 0,-2-2 0,1-1 0,-2-1 0,29-25 0,-47 35 0,0-1 0,0 1 0,-1-1 0,0 0 0,-1 0 0,0-1 0,0 1 0,0-1 0,1-9 0,-1 5 0,1 1 0,0 0 0,12-20 0,140-199 0,-127 185 0,-21 30 0,0 1 0,23-26 0,-12 15 0,-2-1 0,-1 0 0,0-2 0,-2 0 0,15-43 0,-26 61 0,2-5 0,-1-1 0,-1 0 0,0 0 0,1-28 0,5-24 0,-2 21 0,-3-1 0,-2 0 0,-6-86 0,0 26 0,3 30-1365,0 56-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.6">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.59">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1552.66">7387 135 24575,'3'1'0,"-1"-1"0,1 2 0,0-1 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 0 0,2 3 0,23 31 0,26 70 0,43 76 0,-6-49 0,-86-126-83,4 8-173,0 0-1,2 0 1,0-1-1,21 25 1,-19-28-6570</inkml:trace>
 </inkml:ink>
 </file>
@@ -8021,11 +8523,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>0.13054187192118227</v>
+        <v>0.12990196078431374</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -8065,7 +8567,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8130,11 +8632,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.53488372093023251</v>
+        <v>-0.53179190751445082</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8161,11 +8663,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.60526315789473684</v>
+        <v>-0.60130718954248363</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -8192,11 +8694,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.65248226950354615</v>
+        <v>-0.647887323943662</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -9746,11 +10248,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0.10837438423645321</v>
+        <v>0.10784313725490197</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -9768,7 +10270,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -9789,11 +10291,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-1.0526315789473684</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -9806,11 +10308,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-1.6666666666666667</v>
+        <v>-1.5384615384615385</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -9823,11 +10325,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -12258,6 +12760,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101009C7952A5A25B2543AB99BC9B879A46ED" ma:contentTypeVersion="16" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="18ce886227b4f7d0c1a56646945dc47e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xmlns:ns3="04574505-c322-4981-8ebb-5d25af8d4de8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5be0a050d98fc17aa9c3986a154fc28" ns2:_="" ns3:_="">
     <xsd:import namespace="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
@@ -12500,15 +13011,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -12521,6 +13023,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F472F951-64CD-40D8-896F-068DA14071AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12537,12 +13047,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Summer2コスト表_井上恋.xlsx
+++ b/Summer2コスト表_井上恋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r_inoue\Documents\GitHub\Summer2_ChangeCollidable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC35B42A-FFC2-4A36-9962-E4D0BBB3277A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F369FBC0-4AAF-4506-9FAE-C146105E125A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2745" windowWidth="21600" windowHeight="12645" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3885" yWindow="3495" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="クラス設計" sheetId="6" r:id="rId5"/>
     <sheet name="クラス図" sheetId="7" r:id="rId6"/>
     <sheet name="敵のグループ化" sheetId="9" r:id="rId7"/>
+    <sheet name="ノーマルカメラ" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="292">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -2141,6 +2142,30 @@
   </si>
   <si>
     <t>作業中</t>
+  </si>
+  <si>
+    <t>プレイヤーのX座標 + 500</t>
+    <rPh sb="7" eb="9">
+      <t>ザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのX座標 - 500</t>
+    <rPh sb="7" eb="9">
+      <t>ザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラのX座標 + プレイヤーの進行方向</t>
+    <rPh sb="5" eb="7">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>シンコウホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -8110,6 +8135,483 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="グループ化 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1990573-BEAC-0520-32FA-C1D75677503E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3800475" y="1457325"/>
+          <a:ext cx="400050" cy="1066800"/>
+          <a:chOff x="3800475" y="1457325"/>
+          <a:chExt cx="400050" cy="1066800"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="スマイル 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C362D506-BDCE-E13C-D3F2-383871C170BA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3829050" y="1457325"/>
+            <a:ext cx="342900" cy="333375"/>
+          </a:xfrm>
+          <a:prstGeom prst="smileyFace">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="二等辺三角形 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0208D206-0D31-1758-B10B-BA90EBE54119}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3800475" y="1819275"/>
+            <a:ext cx="400050" cy="704850"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4764239-D803-D720-B9D3-81D11422BF86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4171950" y="1943100"/>
+          <a:ext cx="1762125" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45E40EEA-822F-4EDD-94C0-665C91311F60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2324100" y="1943100"/>
+          <a:ext cx="1485900" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0211C04-4418-69D3-54E1-5BD2BA88D17F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2266950" y="371475"/>
+          <a:ext cx="0" cy="2962275"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A5EB29C-0EAC-4C66-A76C-16D9EB13FDDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5943600" y="381000"/>
+          <a:ext cx="0" cy="2962275"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="15" name="グループ化 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3884848-41D4-2655-1547-43B89A1808AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="885825" y="914400"/>
+          <a:ext cx="2809875" cy="1962150"/>
+          <a:chOff x="876300" y="885825"/>
+          <a:chExt cx="2809875" cy="1962150"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="正方形/長方形 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17C173A9-09ED-22E6-6C1A-3E714F478061}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="876300" y="885825"/>
+            <a:ext cx="2809875" cy="1962150"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="76200" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="none" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="accent2"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="楕円 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8AD4822-85B6-67C5-693C-CB085164B0BC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2105024" y="1752599"/>
+            <a:ext cx="333375" cy="333375"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -8165,7 +8667,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">3654 2265 24575,'-31'0'0,"-1"1"0,1 2 0,-44 9 0,27-5 0,0-2 0,0-1 0,-90-7 0,32 0 0,-107 17 0,-9-1 0,-473-14-570,663-1 570,0-1 0,0-2 0,-42-11 0,39 7 0,0 2 0,-46-4 0,2 4-296,-124-29-1,100 15 365,24 6-68,0-2 0,-109-41 0,33 1-99,-142-63-168,243 94-776,8 4-1413,-54-34 0,47 23 3124,28 18 685,1 0-1,-40-34 1,58 43-1146,-1-1 0,1 0 0,0 0 0,0-1 0,1 1 0,0-1 0,1 0 0,-1 0-1,1-1 1,1 0 0,0 1 0,-4-18 0,5 14-207,-8-36 0,2 0 0,-2-84 0,10 117 0,0-25 0,9-68 0,-7 94 0,1 0 0,1 0 0,0 1 0,1-1 0,1 1 0,0 0 0,0 1 0,13-18 0,23-32-452,64-83 1134,-88 123-2643,2 2 0,28-24 0,41-35 347,28-23 1558,-19 35 1888,2 4 0,188-87 0,-178 104-2326,2 5 0,1 4 0,131-23 0,-138 33-2142,-63 15 1568,1 2-1,55-6 1,90-1 963,479-21-635,-504 37 1171,239 9-1340,-327-3 2278,0 5 0,-1 2 0,93 29 1,-56-9-509,-49-16 1,0 4 1,75 34-1,-32-2-793,-2 5 0,96 70 0,-123-66 873,89 91 0,-140-126-991,35 33 49,103 128 0,-45-10 0,-106-155 0,0 1 0,-2 0 0,-1 1 0,-1 0 0,0 1 0,-2 0 0,7 47 0,-3-8 0,-6-36 0,0 0 0,0 37 0,-4 7-1213,-4 124-4358,-1-163 5571,-1 0 0,-16 56 0,-39 48-756,53-117 1900,-1-1 1,0-1-1,-1 1 0,-1-1 0,-1-1 0,-18 23 1,-18 16-1615,31-42 470,1 0 0,-2-1 0,0 0 0,0-2 0,-1 0 0,-33 14 0,-138 66 0,165-80 0,-1-2 0,0 0 0,0-2 0,-47 8 0,34-7 0,-42 13 0,11 4 0,20-7 0,-73 18 0,43-12 0,61-17 0,0-1 0,-1 0 0,-29 3 0,-31 4 0,54-8 0,0-1 0,-30 0 0,45-4 0,0 0 0,0-1 0,0-1 0,0 1 0,0-2 0,0 1 0,1-1 0,-1-1 0,-9-5 0,-27-13-109,7 3-310,2-1 1,-65-45-1,86 52-6407</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="809.61">5190 1439 24575,'8'1'0,"1"0"0,0 1 0,-1 0 0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,0 1 0,-1-1 0,0 1 0,12 10 0,42 24 0,10 0 0,-45-24 0,44 19 0,-53-27 0,0 0 0,0-1 0,1-2 0,0 1 0,0-2 0,0-1 0,19 1 0,-2-1 0,-1 2 0,65 16 0,-65-11 0,1-2 0,62 4 0,-94-11 0,64 2 0,0-3 0,126-18 0,-105 3 0,-22 5 0,91-28 0,-129 29 0,-1-2 0,0 0 0,0-1 0,-2-2 0,1-1 0,-2-1 0,29-25 0,-47 35 0,0-1 0,0 1 0,-1-1 0,0 0 0,-1 0 0,0-1 0,0 1 0,0-1 0,1-9 0,-1 5 0,1 1 0,0 0 0,12-20 0,140-199 0,-127 185 0,-21 30 0,0 1 0,23-26 0,-12 15 0,-2-1 0,-1 0 0,0-2 0,-2 0 0,15-43 0,-26 61 0,2-5 0,-1-1 0,-1 0 0,0 0 0,1-28 0,5-24 0,-2 21 0,-3-1 0,-2 0 0,-6-86 0,0 26 0,3 30-1365,0 56-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.59">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1173.58">7387 54 24575,'-2'1'0,"1"-1"0,-1 0 0,1 1 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,-1 3 0,-18 29 0,13-22 0,-86 157 0,46-105 25,38-54-199,1 1 1,-1 1-1,2 0 0,0 0 0,0 0 0,1 1 1,-10 24-1,12-17-6652</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1552.66">7387 135 24575,'3'1'0,"-1"-1"0,1 2 0,0-1 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 1 0,-1 0 0,0 0 0,0 0 0,0 0 0,2 3 0,23 31 0,26 70 0,43 76 0,-6-49 0,-86-126-83,4 8-173,0 0-1,2 0 1,0-1-1,21 25 1,-19-28-6570</inkml:trace>
 </inkml:ink>
 </file>
@@ -8523,11 +9025,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>0.12990196078431374</v>
+        <v>0.12926829268292683</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -8567,7 +9069,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45888</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8632,11 +9134,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-173</v>
+        <v>-174</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.53179190751445082</v>
+        <v>-0.52873563218390807</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -8663,11 +9165,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.60130718954248363</v>
+        <v>-0.59740259740259738</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -8694,11 +9196,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.647887323943662</v>
+        <v>-0.64335664335664333</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -10248,11 +10750,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0.10784313725490197</v>
+        <v>0.10731707317073171</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -10270,7 +10772,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45888</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -10291,11 +10793,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-1</v>
+        <v>-0.95238095238095233</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -10308,11 +10810,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-1.5384615384615385</v>
+        <v>-1.4285714285714286</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -10325,11 +10827,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>5</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -12747,6 +13249,35 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D42409F-30D3-44A5-B22A-8EF5A7359940}">
+  <dimension ref="C3:K15"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="3" spans="3:11">
+      <c r="F3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11">
+      <c r="C15" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="I15" s="84" t="s">
+        <v>289</v>
+      </c>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12760,15 +13291,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101009C7952A5A25B2543AB99BC9B879A46ED" ma:contentTypeVersion="16" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="18ce886227b4f7d0c1a56646945dc47e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xmlns:ns3="04574505-c322-4981-8ebb-5d25af8d4de8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5be0a050d98fc17aa9c3986a154fc28" ns2:_="" ns3:_="">
     <xsd:import namespace="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
@@ -13011,6 +13533,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
@@ -13023,14 +13554,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F472F951-64CD-40D8-896F-068DA14071AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13047,4 +13570,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Summer2コスト表_井上恋.xlsx
+++ b/Summer2コスト表_井上恋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r_inoue\Documents\GitHub\Summer2_ChangeCollidable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F369FBC0-4AAF-4506-9FAE-C146105E125A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6247BD-413B-47D3-A1E5-0868649F0897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="3495" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21615" yWindow="2385" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="クラス図" sheetId="7" r:id="rId6"/>
     <sheet name="敵のグループ化" sheetId="9" r:id="rId7"/>
     <sheet name="ノーマルカメラ" sheetId="10" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="296">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -2164,6 +2165,52 @@
     </rPh>
     <rPh sb="16" eb="20">
       <t>シンコウホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生成した際にエリアを作成</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲の外に出たら中心に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>or</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あらかじめエリアを作ってその中をウロウロする</t>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5094,13 +5141,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>652463</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>644670</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>214745</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>661988</xdr:colOff>
+      <xdr:colOff>655926</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
@@ -5114,14 +5161,13 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
           <a:endCxn id="7" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6291263" y="1590675"/>
-          <a:ext cx="9525" cy="447675"/>
+        <a:xfrm>
+          <a:off x="6325034" y="1998518"/>
+          <a:ext cx="11256" cy="906607"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5278,15 +5324,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>526676</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>75079</xdr:rowOff>
+      <xdr:colOff>578629</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>23124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>345701</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>65554</xdr:rowOff>
+      <xdr:colOff>397654</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>13599</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5301,8 +5347,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5468470" y="3548903"/>
-          <a:ext cx="1869702" cy="696445"/>
+          <a:off x="5566265" y="5062715"/>
+          <a:ext cx="1897207" cy="717839"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5454,15 +5500,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>651342</xdr:colOff>
+      <xdr:colOff>675409</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>69271</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>94409</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>75079</xdr:rowOff>
+      <xdr:colOff>141778</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>23124</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5474,14 +5520,13 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="2"/>
           <a:endCxn id="14" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6276695" y="2805953"/>
-          <a:ext cx="126626" cy="742950"/>
+          <a:off x="6355773" y="4139044"/>
+          <a:ext cx="159096" cy="923671"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6195,13 +6240,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>96010</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>65554</xdr:rowOff>
+      <xdr:colOff>141778</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>13599</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>247168</xdr:colOff>
+      <xdr:colOff>247167</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>48025</xdr:rowOff>
     </xdr:to>
@@ -6221,8 +6266,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6382510" y="4583125"/>
-          <a:ext cx="151158" cy="2186829"/>
+          <a:off x="6514869" y="5780554"/>
+          <a:ext cx="105389" cy="2407016"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6789,6 +6834,69 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>242454</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>519546</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139362</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="正方形/長方形 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F85F20C0-177F-4EFB-876B-BC2A1875DA16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14114318" y="4623955"/>
+          <a:ext cx="3740728" cy="1039907"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>アクションを管理する</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -8612,6 +8720,1250 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>400049</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="楕円 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC41E9E-85D8-6505-1C7C-A7AA9A54A035}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3143249" y="3971925"/>
+          <a:ext cx="8648701" cy="857250"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E468E183-2639-9B9D-1633-E414B3D58C3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2762250" y="1143000"/>
+          <a:ext cx="1200150" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="楕円 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E348A401-2088-4DC4-863E-287C1A779CD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2714625" y="2181225"/>
+          <a:ext cx="5534025" cy="561975"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="楕円 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59C6F5D4-9244-D8AB-8064-1B453B918557}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5219700" y="1981200"/>
+          <a:ext cx="504825" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="グループ化 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{986FB8B7-7E3F-26C9-B13D-2BB62444D9AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="13563600" y="2314574"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="二等辺三角形 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DABC0821-B222-259A-1019-03562F84C27B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="楕円 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{946AE95B-EE4B-A302-DF29-CA2946F2F301}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="11" name="グループ化 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF051CC2-0E87-4F75-B2C7-26E01CBED7E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="13563600" y="1019175"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="二等辺三角形 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34812565-B5F5-7CA0-5925-FBA806AA7382}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="楕円 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE6A6F43-19E2-1C29-B898-56425FE66A9D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="14" name="グループ化 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7702CDF0-CA21-4197-B803-DFE02B1445F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="11944350" y="3105150"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="二等辺三角形 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC4E6548-7D52-B5C6-B44D-A2210A21E0AA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="楕円 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEBD408B-19A2-DB0A-1645-A0880077B4A4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="17" name="グループ化 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E94DBC64-1053-4787-A5BB-8DD209D16068}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12773025" y="2352675"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="二等辺三角形 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7ED3D2-5CE2-CA7D-D7D4-D8CC78BD32BB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="19" name="楕円 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4306C0CE-4110-4C59-453F-CF36670FA0C1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="20" name="グループ化 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CAF385C-9734-4E7A-A0DA-1CD26B162392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="11982450" y="1695450"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="二等辺三角形 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EEF0760-8943-473E-5783-7AB54AFDA54E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="22" name="楕円 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C45717E-3488-9B0E-C33B-FA9CC36852E0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="23" name="グループ化 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF010BAD-577B-4264-897A-9CF8C39CC078}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12677775" y="990600"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="24" name="二等辺三角形 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65226AC4-0538-74F5-EB21-B0F78D8CA620}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="楕円 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1583C73F-12EB-1382-7E07-C939822CA8AB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="26" name="グループ化 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C101ECE-616E-4240-8F12-014B651690E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6781800" y="1504950"/>
+          <a:ext cx="628650" cy="1009650"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="二等辺三角形 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{494FC995-47BA-A58C-7FD7-FA06FE401A36}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="28" name="楕円 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94DF33B7-E91D-9D3F-9E26-D31DBE8F5C5F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>228601</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="29" name="グループ化 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7953B8B-7633-4455-BA1F-785FA04BFB64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="14668500" y="1552575"/>
+          <a:ext cx="628650" cy="1057276"/>
+          <a:chOff x="4019550" y="1162049"/>
+          <a:chExt cx="628650" cy="1057276"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="30" name="二等辺三角形 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC37890-63C9-B1D8-EB82-C4810C83F3A7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4019550" y="1504950"/>
+            <a:ext cx="628650" cy="714375"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="31" name="楕円 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF14FB1A-1586-C740-C286-ED574A6F760E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095749" y="1162049"/>
+            <a:ext cx="476251" cy="466725"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -9025,11 +10377,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>0.12926829268292683</v>
+        <v>0.12864077669902912</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9069,7 +10421,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45889</v>
+        <v>45890</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9134,11 +10486,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-174</v>
+        <v>-175</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.52873563218390807</v>
+        <v>-0.52571428571428569</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -9165,11 +10517,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-154</v>
+        <v>-155</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.59740259740259738</v>
+        <v>-0.59354838709677415</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -9196,11 +10548,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.64335664335664333</v>
+        <v>-0.63888888888888884</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -10750,11 +12102,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0.10731707317073171</v>
+        <v>0.10679611650485436</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -10772,7 +12124,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45889</v>
+        <v>45890</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -10793,11 +12145,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.95238095238095233</v>
+        <v>-0.90909090909090906</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -10810,11 +12162,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-1.4285714285714286</v>
+        <v>-1.3333333333333333</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -10827,11 +12179,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -13278,16 +14630,41 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9717BA7D-F47C-47CA-887E-908DE13C8EE4}">
+  <dimension ref="D5:L8"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="5" spans="4:12">
+      <c r="D5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G5" t="s">
+        <v>294</v>
+      </c>
+      <c r="H5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" spans="4:12">
+      <c r="L8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
-    <_x8a73__x7d30_ xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13534,21 +14911,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
+    <_x8a73__x7d30_ xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
-    <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13573,9 +14950,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
+    <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Summer2コスト表_井上恋.xlsx
+++ b/Summer2コスト表_井上恋.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r_inoue\Documents\GitHub\Summer2_ChangeCollidable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lovecap\Documents\GitHub\Summer2_ChangeCollidable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6247BD-413B-47D3-A1E5-0868649F0897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F9C3BC-9208-4F84-A2BE-B0490AB30E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21615" yWindow="2385" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$84</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="292">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -975,9 +975,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未着手</t>
-  </si>
-  <si>
     <t>全体の作業項目数</t>
   </si>
   <si>
@@ -1124,9 +1121,6 @@
     <t>画面遷移</t>
   </si>
   <si>
-    <t>先行入力</t>
-  </si>
-  <si>
     <t>ビルドテスト</t>
   </si>
   <si>
@@ -1408,19 +1402,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーへの操作を促すボタンを主張させる</t>
-    <rPh sb="7" eb="9">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ウナガ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>シュチョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BOSS1</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2140,9 +2121,6 @@
       <t>カン</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中</t>
   </si>
   <si>
     <t>プレイヤーのX座標 + 500</t>
@@ -10377,11 +10355,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>0.12864077669902912</v>
+        <v>0.11422413793103449</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -10421,7 +10399,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45890</v>
+        <v>45928</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -10486,11 +10464,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-175</v>
+        <v>-201</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.52571428571428569</v>
+        <v>-0.45771144278606968</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -10517,11 +10495,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-155</v>
+        <v>-181</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.59354838709677415</v>
+        <v>-0.50828729281767959</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -10548,11 +10526,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-144</v>
+        <v>-170</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.63888888888888884</v>
+        <v>-0.54117647058823526</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -12080,8 +12058,8 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F116)</f>
-        <v>42</v>
+        <f>SUM(作業工数見積もり!F3:F114)</f>
+        <v>41.25</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -12102,11 +12080,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0.10679611650485436</v>
+        <v>9.4827586206896547E-2</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -12124,7 +12102,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45890</v>
+        <v>45928</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -12145,11 +12123,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-22</v>
+        <v>-48</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-0.90909090909090906</v>
+        <v>-0.40104166666666669</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -12162,11 +12140,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-15</v>
+        <v>-41</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-1.3333333333333333</v>
+        <v>-0.46951219512195119</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -12179,11 +12157,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>2</v>
+        <v>-26</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>10</v>
+        <v>-0.74038461538461542</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -12266,8 +12244,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="B2:M87"/>
+  <dimension ref="B2:M85"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="33"/>
   <cols>
     <col min="1" max="1" width="9.75" style="26"/>
@@ -12313,7 +12290,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>133</v>
@@ -12328,25 +12305,25 @@
         <v>0.25</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I3" s="34"/>
       <c r="J3" s="35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K3" s="36">
         <f>SUM(K4,K5,K6)</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L3" s="37"/>
       <c r="M3" s="38"/>
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D4" s="27" t="s">
         <v>9</v>
@@ -12358,14 +12335,14 @@
         <v>0.25</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="39" t="s">
         <v>126</v>
       </c>
       <c r="K4" s="40">
-        <f>COUNTIF(E3:E84,J4)</f>
+        <f>COUNTIF(E3:E82,J4)</f>
         <v>40</v>
       </c>
       <c r="L4" s="41"/>
@@ -12373,10 +12350,10 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>9</v>
@@ -12388,14 +12365,14 @@
         <v>0.25</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I5" s="34"/>
       <c r="J5" s="42" t="s">
         <v>1</v>
       </c>
       <c r="K5" s="40">
-        <f>COUNTIF(E3:E84,J5)</f>
+        <f>COUNTIF(E3:E82,J5)</f>
         <v>38</v>
       </c>
       <c r="L5" s="41"/>
@@ -12403,10 +12380,10 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" s="27" t="s">
         <v>9</v>
@@ -12418,25 +12395,25 @@
         <v>0.5</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I6" s="34"/>
       <c r="J6" s="43" t="s">
         <v>127</v>
       </c>
       <c r="K6" s="40">
-        <f>COUNTIF(E3:E84,J6)</f>
-        <v>4</v>
+        <f>COUNTIF(E3:E82,J6)</f>
+        <v>2</v>
       </c>
       <c r="L6" s="41"/>
       <c r="M6" s="38"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>9</v>
@@ -12448,28 +12425,28 @@
         <v>1</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I7" s="34"/>
       <c r="J7" s="44" t="s">
         <v>35</v>
       </c>
       <c r="K7" s="40">
-        <f>COUNTIF(H3:H84,J7)</f>
-        <v>76</v>
+        <f>COUNTIF(H3:H82,J7)</f>
+        <v>80</v>
       </c>
       <c r="L7" s="45">
         <f>K7/K3</f>
-        <v>0.92682926829268297</v>
+        <v>1</v>
       </c>
       <c r="M7" s="38"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D8" s="27" t="s">
         <v>9</v>
@@ -12481,28 +12458,28 @@
         <v>2</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K8" s="40">
-        <f>COUNTIF(H3:H84,J8)</f>
-        <v>3</v>
+        <f>COUNTIF(H3:H82,J8)</f>
+        <v>0</v>
       </c>
       <c r="L8" s="47">
         <f>(K8+K9)/K3</f>
-        <v>7.3170731707317069E-2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="38"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>9</v>
@@ -12517,25 +12494,25 @@
         <v>0.25</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I9" s="34"/>
       <c r="J9" s="49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K9" s="31">
-        <f>COUNTIF(H3:H84,J9)</f>
-        <v>3</v>
+        <f>COUNTIF(H3:H82,J9)</f>
+        <v>0</v>
       </c>
       <c r="L9" s="41"/>
       <c r="M9" s="38"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>9</v>
@@ -12547,7 +12524,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I10" s="34"/>
       <c r="J10" s="50"/>
@@ -12557,10 +12534,10 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>9</v>
@@ -12575,25 +12552,25 @@
         <v>0.25</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I11" s="34"/>
       <c r="J11" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K11" s="31">
-        <f>SUM(F3:F84)</f>
-        <v>41.75</v>
+        <f>SUM(F3:F82)</f>
+        <v>41</v>
       </c>
       <c r="L11" s="41"/>
       <c r="M11" s="38"/>
     </row>
     <row r="12" spans="2:13" ht="33.75" thickBot="1">
       <c r="B12" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D12" s="27" t="s">
         <v>9</v>
@@ -12608,25 +12585,25 @@
         <v>0.25</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I12" s="34"/>
       <c r="J12" s="52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K12" s="53">
         <f>8*K11</f>
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L12" s="54"/>
       <c r="M12" s="38"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D13" s="27" t="s">
         <v>9</v>
@@ -12638,7 +12615,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J13" s="55"/>
       <c r="K13" s="56"/>
@@ -12646,10 +12623,10 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>145</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>146</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>9</v>
@@ -12661,15 +12638,15 @@
         <v>0.25</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>9</v>
@@ -12681,15 +12658,15 @@
         <v>0.25</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>9</v>
@@ -12701,15 +12678,15 @@
         <v>0.25</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>9</v>
@@ -12724,15 +12701,15 @@
         <v>0.25</v>
       </c>
       <c r="H17" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D18" s="27" t="s">
         <v>9</v>
@@ -12747,15 +12724,15 @@
         <v>0.5</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>9</v>
@@ -12767,15 +12744,15 @@
         <v>1</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D20" s="27" t="s">
         <v>9</v>
@@ -12787,15 +12764,15 @@
         <v>1</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>9</v>
@@ -12807,15 +12784,15 @@
         <v>1</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D22" s="27" t="s">
         <v>9</v>
@@ -12827,15 +12804,15 @@
         <v>0.5</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D23" s="27" t="s">
         <v>9</v>
@@ -12847,15 +12824,15 @@
         <v>0.25</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D24" s="27" t="s">
         <v>9</v>
@@ -12867,15 +12844,15 @@
         <v>0.5</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D25" s="27" t="s">
         <v>9</v>
@@ -12887,15 +12864,15 @@
         <v>1</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D26" s="27" t="s">
         <v>9</v>
@@ -12907,15 +12884,15 @@
         <v>0.5</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D27" s="27" t="s">
         <v>9</v>
@@ -12927,15 +12904,15 @@
         <v>0.25</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="59" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>9</v>
@@ -12947,15 +12924,15 @@
         <v>0.25</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="59" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D29" s="27" t="s">
         <v>9</v>
@@ -12967,15 +12944,15 @@
         <v>0.5</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="59" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>9</v>
@@ -12987,15 +12964,15 @@
         <v>0.25</v>
       </c>
       <c r="H30" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>176</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>178</v>
       </c>
       <c r="D31" s="27" t="s">
         <v>9</v>
@@ -13007,15 +12984,15 @@
         <v>0.25</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="59" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D32" s="27" t="s">
         <v>9</v>
@@ -13030,15 +13007,15 @@
         <v>0.25</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="60" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D33" s="27" t="s">
         <v>9</v>
@@ -13050,15 +13027,15 @@
         <v>0.5</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="60" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D34" s="27" t="s">
         <v>9</v>
@@ -13070,15 +13047,15 @@
         <v>0.5</v>
       </c>
       <c r="H34" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" s="60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>9</v>
@@ -13090,15 +13067,15 @@
         <v>0.5</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="60" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D36" s="27" t="s">
         <v>9</v>
@@ -13110,15 +13087,15 @@
         <v>0.5</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="60" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>9</v>
@@ -13130,15 +13107,15 @@
         <v>0.5</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="60" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D38" s="27" t="s">
         <v>9</v>
@@ -13150,15 +13127,15 @@
         <v>0.5</v>
       </c>
       <c r="H38" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="60" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>9</v>
@@ -13170,15 +13147,15 @@
         <v>0.5</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="60" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D40" s="27" t="s">
         <v>9</v>
@@ -13190,15 +13167,15 @@
         <v>0.5</v>
       </c>
       <c r="H40" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="60" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>9</v>
@@ -13210,15 +13187,15 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="60" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D42" s="27" t="s">
         <v>9</v>
@@ -13230,15 +13207,15 @@
         <v>0.5</v>
       </c>
       <c r="H42" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="60" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>9</v>
@@ -13250,15 +13227,15 @@
         <v>1</v>
       </c>
       <c r="H43" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="61" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D44" s="27" t="s">
         <v>17</v>
@@ -13270,15 +13247,15 @@
         <v>0.25</v>
       </c>
       <c r="H44" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="61" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>17</v>
@@ -13290,15 +13267,15 @@
         <v>0.25</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="C46" s="26" t="s">
         <v>215</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>218</v>
       </c>
       <c r="D46" s="27" t="s">
         <v>9</v>
@@ -13310,15 +13287,15 @@
         <v>0.5</v>
       </c>
       <c r="H46" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="61" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>17</v>
@@ -13330,15 +13307,15 @@
         <v>0.25</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="26" t="s">
         <v>150</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>151</v>
       </c>
       <c r="D48" s="27" t="s">
         <v>9</v>
@@ -13353,15 +13330,15 @@
         <v>0.25</v>
       </c>
       <c r="H48" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>9</v>
@@ -13376,15 +13353,15 @@
         <v>0.5</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" hidden="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
       <c r="B50" s="62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D50" s="27" t="s">
         <v>9</v>
@@ -13396,15 +13373,15 @@
         <v>0.5</v>
       </c>
       <c r="H50" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="2:8">
       <c r="B51" s="63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>9</v>
@@ -13416,15 +13393,15 @@
         <v>1</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>9</v>
@@ -13436,15 +13413,15 @@
         <v>1</v>
       </c>
       <c r="H52" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D53" s="27" t="s">
         <v>9</v>
@@ -13456,15 +13433,15 @@
         <v>1</v>
       </c>
       <c r="H53" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D54" s="27" t="s">
         <v>9</v>
@@ -13476,15 +13453,15 @@
         <v>1</v>
       </c>
       <c r="H54" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>9</v>
@@ -13496,15 +13473,15 @@
         <v>1</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D56" s="27" t="s">
         <v>9</v>
@@ -13516,15 +13493,15 @@
         <v>0.5</v>
       </c>
       <c r="H56" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="26" t="s">
         <v>155</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>156</v>
       </c>
       <c r="D57" s="27" t="s">
         <v>17</v>
@@ -13536,15 +13513,15 @@
         <v>0.25</v>
       </c>
       <c r="H57" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D58" s="27" t="s">
         <v>17</v>
@@ -13556,15 +13533,15 @@
         <v>0.25</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" hidden="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
       <c r="B59" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D59" s="27" t="s">
         <v>17</v>
@@ -13576,15 +13553,15 @@
         <v>0.25</v>
       </c>
       <c r="H59" s="27" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D60" s="27" t="s">
         <v>9</v>
@@ -13596,15 +13573,15 @@
         <v>0.5</v>
       </c>
       <c r="H60" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>17</v>
@@ -13616,15 +13593,15 @@
         <v>0.25</v>
       </c>
       <c r="H61" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="B62" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="26" t="s">
         <v>185</v>
-      </c>
-      <c r="C62" s="26" t="s">
-        <v>187</v>
       </c>
       <c r="D62" s="27" t="s">
         <v>17</v>
@@ -13636,15 +13613,15 @@
         <v>0.25</v>
       </c>
       <c r="H62" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>25</v>
@@ -13656,15 +13633,15 @@
         <v>0.25</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>288</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D64" s="27" t="s">
         <v>9</v>
@@ -13676,15 +13653,15 @@
         <v>0.25</v>
       </c>
       <c r="H64" s="27" t="s">
-        <v>288</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="2:8">
       <c r="B65" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>9</v>
@@ -13696,15 +13673,15 @@
         <v>1</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D66" s="27" t="s">
         <v>9</v>
@@ -13716,15 +13693,15 @@
         <v>1</v>
       </c>
       <c r="H66" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D67" s="27" t="s">
         <v>9</v>
@@ -13736,15 +13713,15 @@
         <v>1</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D68" s="27" t="s">
         <v>9</v>
@@ -13756,15 +13733,15 @@
         <v>0.25</v>
       </c>
       <c r="H68" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" s="66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>9</v>
@@ -13776,15 +13753,15 @@
         <v>0.25</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>288</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="B70" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D70" s="27" t="s">
         <v>9</v>
@@ -13796,15 +13773,15 @@
         <v>0.25</v>
       </c>
       <c r="H70" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D71" s="27" t="s">
         <v>9</v>
@@ -13816,15 +13793,15 @@
         <v>0.5</v>
       </c>
       <c r="H71" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D72" s="27" t="s">
         <v>9</v>
@@ -13836,15 +13813,15 @@
         <v>0.5</v>
       </c>
       <c r="H72" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D73" s="27" t="s">
         <v>9</v>
@@ -13856,15 +13833,15 @@
         <v>0.5</v>
       </c>
       <c r="H73" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74" spans="2:8">
       <c r="B74" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D74" s="27" t="s">
         <v>9</v>
@@ -13876,15 +13853,15 @@
         <v>0.5</v>
       </c>
       <c r="H74" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="2:8">
       <c r="B75" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D75" s="27" t="s">
         <v>9</v>
@@ -13896,15 +13873,15 @@
         <v>0.5</v>
       </c>
       <c r="H75" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" spans="2:8">
       <c r="B76" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="26" t="s">
         <v>161</v>
-      </c>
-      <c r="C76" s="26" t="s">
-        <v>162</v>
       </c>
       <c r="D76" s="27" t="s">
         <v>9</v>
@@ -13916,15 +13893,15 @@
         <v>0.25</v>
       </c>
       <c r="H76" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="2:8">
       <c r="B77" s="68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D77" s="27" t="s">
         <v>9</v>
@@ -13936,15 +13913,15 @@
         <v>0.25</v>
       </c>
       <c r="H77" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="2:8">
       <c r="B78" s="68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C78" s="30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D78" s="27" t="s">
         <v>25</v>
@@ -13956,35 +13933,35 @@
         <v>0.5</v>
       </c>
       <c r="H78" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" hidden="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
       <c r="B79" s="68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F79" s="27">
         <v>0.5</v>
       </c>
       <c r="H79" s="27" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="2:8">
-      <c r="B80" s="68" t="s">
-        <v>161</v>
+      <c r="B80" s="57" t="s">
+        <v>137</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="D80" s="27" t="s">
         <v>9</v>
@@ -13993,35 +13970,35 @@
         <v>18</v>
       </c>
       <c r="F80" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="H80" s="27" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
+      <c r="B81" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C81" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" s="27">
         <v>0.5</v>
       </c>
-      <c r="H80" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" hidden="1">
-      <c r="B81" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="C81" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F81" s="27">
-        <v>0.25</v>
-      </c>
       <c r="H81" s="27" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C82" s="26" t="s">
         <v>188</v>
@@ -14036,12 +14013,12 @@
         <v>0.25</v>
       </c>
       <c r="H82" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="2:8">
       <c r="B83" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C83" s="26" t="s">
         <v>189</v>
@@ -14053,78 +14030,31 @@
         <v>18</v>
       </c>
       <c r="F83" s="27">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H83" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="84" spans="2:8">
-      <c r="B84" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="C84" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D84" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F84" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="H84" s="27" t="s">
-        <v>222</v>
+      <c r="B84" s="26" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="C85" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="D85" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="H85" s="27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" hidden="1">
-      <c r="B86" s="26" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8">
-      <c r="H87" s="69"/>
+      <c r="H85" s="69"/>
     </row>
   </sheetData>
-  <autoFilter ref="C2:H86" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="アルファ"/>
-        <filter val="プロト"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C2:H84" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D86" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D84" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E86" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E84" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H86" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H84" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14140,25 +14070,25 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="94" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="94" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" s="94" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="F2" s="94" t="s">
         <v>281</v>
       </c>
-      <c r="D2" s="94" t="s">
+      <c r="G2" s="94" t="s">
         <v>282</v>
       </c>
-      <c r="E2" s="94" t="s">
+      <c r="H2" s="94" t="s">
         <v>283</v>
-      </c>
-      <c r="F2" s="94" t="s">
-        <v>284</v>
-      </c>
-      <c r="G2" s="94" t="s">
-        <v>285</v>
-      </c>
-      <c r="H2" s="94" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="3" spans="2:8">
@@ -14278,7 +14208,7 @@
     </row>
     <row r="19" spans="6:6">
       <c r="F19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -14305,148 +14235,148 @@
     <row r="2" spans="2:8" ht="19.5" thickBot="1">
       <c r="B2" s="70"/>
       <c r="C2" s="71" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="73" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F3" s="79" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="73"/>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D4" s="74" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F4" s="80" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19.5" thickBot="1">
       <c r="B5" s="73"/>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F5" s="81" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="19.5" thickBot="1">
       <c r="B6" s="75"/>
       <c r="C6" s="76" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F6" s="78" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="D8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="C9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="F10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="19.5" thickBot="1">
       <c r="F11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="70"/>
       <c r="C12" s="71" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D12" s="72" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="73" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D13" s="74" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="73"/>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D14" s="74" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="73"/>
       <c r="C15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D15" s="74" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="19.5" thickBot="1">
       <c r="B16" s="75"/>
       <c r="C16" s="76" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -14469,12 +14399,12 @@
   <sheetData>
     <row r="2" spans="5:27">
       <c r="E2" s="82" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="5:27" ht="25.5">
       <c r="L4" s="83" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="U4" s="89"/>
       <c r="V4" s="89"/>
@@ -14486,10 +14416,10 @@
     </row>
     <row r="5" spans="5:27" ht="57.75">
       <c r="E5" s="88" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q5" s="92" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="R5" s="93"/>
       <c r="S5" s="93"/>
@@ -14499,7 +14429,7 @@
       <c r="X5" s="89"/>
       <c r="Y5" s="89"/>
       <c r="Z5" s="90" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AA5" s="89"/>
     </row>
@@ -14523,7 +14453,7 @@
     </row>
     <row r="8" spans="5:27" ht="45.75">
       <c r="I8" s="84" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="U8" s="89"/>
       <c r="V8" s="89"/>
@@ -14531,16 +14461,16 @@
       <c r="X8" s="89"/>
       <c r="Y8" s="89"/>
       <c r="Z8" s="91" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AA8" s="89"/>
     </row>
     <row r="9" spans="5:27" ht="30">
       <c r="L9" s="83" t="s">
+        <v>270</v>
+      </c>
+      <c r="R9" s="92" t="s">
         <v>273</v>
-      </c>
-      <c r="R9" s="92" t="s">
-        <v>276</v>
       </c>
       <c r="S9" s="93"/>
       <c r="T9" s="93"/>
@@ -14554,7 +14484,7 @@
     </row>
     <row r="10" spans="5:27" ht="45.75">
       <c r="R10" s="87" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="U10" s="89"/>
       <c r="V10" s="89"/>
@@ -14562,7 +14492,7 @@
       <c r="X10" s="89"/>
       <c r="Y10" s="89"/>
       <c r="Z10" s="91" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AA10" s="89"/>
     </row>
@@ -14577,7 +14507,7 @@
     </row>
     <row r="25" spans="14:16" ht="33">
       <c r="N25" s="86" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="14:16" ht="39.75">
@@ -14608,17 +14538,17 @@
   <sheetData>
     <row r="3" spans="3:11">
       <c r="F3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="3:11">
       <c r="C15" s="84" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D15" s="84"/>
       <c r="E15" s="84"/>
       <c r="I15" s="84" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J15" s="84"/>
       <c r="K15" s="84"/>
@@ -14637,18 +14567,18 @@
   <sheetData>
     <row r="5" spans="4:12">
       <c r="D5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="H5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="4:12">
       <c r="L8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -14659,15 +14589,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101009C7952A5A25B2543AB99BC9B879A46ED" ma:contentTypeVersion="16" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="18ce886227b4f7d0c1a56646945dc47e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xmlns:ns3="04574505-c322-4981-8ebb-5d25af8d4de8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5be0a050d98fc17aa9c3986a154fc28" ns2:_="" ns3:_="">
     <xsd:import namespace="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
@@ -14910,6 +14831,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -14923,14 +14853,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F472F951-64CD-40D8-896F-068DA14071AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14949,6 +14871,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
